--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,217 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131349617</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>493016</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6676175</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131349603</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>493026</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6676165</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosök nedtill på äldre gran.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131131591</v>
       </c>
       <c r="B2" t="n">
-        <v>57744</v>
+        <v>57746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131349617</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131349603</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131131591</v>
       </c>
       <c r="B2" t="n">
-        <v>57746</v>
+        <v>57747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131349617</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131349603</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131131591</v>
       </c>
       <c r="B2" t="n">
-        <v>57747</v>
+        <v>57748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131349617</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131349603</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131131591</v>
       </c>
       <c r="B2" t="n">
-        <v>57748</v>
+        <v>57751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131349617</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131349603</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131131591</v>
       </c>
       <c r="B2" t="n">
-        <v>57751</v>
+        <v>57752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131349617</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131349603</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131131591</v>
       </c>
       <c r="B2" t="n">
-        <v>57752</v>
+        <v>57757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131349617</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131349603</v>
       </c>
       <c r="B4" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,6 +1001,2195 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131331459</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>493346</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6676152</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131329935</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>493073</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6676217</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Några bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131338781</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>493019</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6676199</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rätt gamla ringhack.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131330073</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>493086</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6676252</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131331376</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>493330</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6676131</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131329898</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57086</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>493071</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6676218</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Under tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131331158</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>493288</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6676274</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131330689</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92288</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>493258</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6676286</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131330685</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57086</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>493255</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6676284</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131331292</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57086</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>493340</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6676251</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131330910</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>493215</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6676275</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131330084</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>493092</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6676215</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131336740</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>493320</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6676280</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131338228</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97274</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>53</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>493275</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6676225</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131329726</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57077</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>492992</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6676226</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Lämplig biotop.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131330626</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57086</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>493203</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6676289</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131332454</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sexberget, Sexberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>493417</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6676274</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131338149</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>493301</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6676186</v>
+      </c>
+      <c r="S22" t="n">
+        <v>9</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131332301</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sexberget, Sexberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>493388</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6676299</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1363,53 +1363,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131330073</v>
+        <v>131331376</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>99034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493086</v>
+        <v>493330</v>
       </c>
       <c r="R8" t="n">
-        <v>6676252</v>
+        <v>6676131</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,81 +1471,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131331376</v>
+        <v>131330073</v>
       </c>
       <c r="B9" t="n">
-        <v>99034</v>
+        <v>5177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493330</v>
+        <v>493086</v>
       </c>
       <c r="R9" t="n">
-        <v>6676131</v>
+        <v>6676252</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,18 +1583,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131330685</v>
+        <v>131331292</v>
       </c>
       <c r="B13" t="n">
         <v>57086</v>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493255</v>
+        <v>493340</v>
       </c>
       <c r="R13" t="n">
-        <v>6676284</v>
+        <v>6676251</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2054,7 +2054,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131331292</v>
+        <v>131330685</v>
       </c>
       <c r="B14" t="n">
         <v>57086</v>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493340</v>
+        <v>493255</v>
       </c>
       <c r="R14" t="n">
-        <v>6676251</v>
+        <v>6676284</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
         <v>131349617</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131349603</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>131331459</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>131329935</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>131338781</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,62 +1363,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131331376</v>
+        <v>131330073</v>
       </c>
       <c r="B8" t="n">
-        <v>99034</v>
+        <v>5178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493330</v>
+        <v>493086</v>
       </c>
       <c r="R8" t="n">
-        <v>6676131</v>
+        <v>6676252</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,71 +1457,81 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131330073</v>
+        <v>131331376</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493086</v>
+        <v>493330</v>
       </c>
       <c r="R9" t="n">
-        <v>6676252</v>
+        <v>6676131</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1570,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,19 +1584,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1605,7 +1605,7 @@
         <v>131329898</v>
       </c>
       <c r="B10" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>131331158</v>
       </c>
       <c r="B11" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>131330689</v>
       </c>
       <c r="B12" t="n">
-        <v>92288</v>
+        <v>92289</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>131331292</v>
       </c>
       <c r="B13" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131330685</v>
       </c>
       <c r="B14" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>131330910</v>
       </c>
       <c r="B15" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>131330084</v>
       </c>
       <c r="B16" t="n">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>97275</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R17" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B18" t="n">
-        <v>97274</v>
+        <v>79261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R18" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,49 +2618,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131329726</v>
+        <v>131330626</v>
       </c>
       <c r="B19" t="n">
-        <v>57077</v>
+        <v>57087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492992</v>
+        <v>493203</v>
       </c>
       <c r="R19" t="n">
-        <v>6676226</v>
+        <v>6676289</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2692,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,19 +2703,19 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Lämplig biotop.</t>
+          <t>Under betad tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2734,50 +2735,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131330626</v>
+        <v>131332454</v>
       </c>
       <c r="B20" t="n">
-        <v>57086</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gräsberget, Gräsberget, Dlr</t>
+          <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493203</v>
+        <v>493417</v>
       </c>
       <c r="R20" t="n">
-        <v>6676289</v>
+        <v>6676274</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2809,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2819,12 +2820,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Under betad tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,53 +2852,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131332454</v>
+        <v>131338149</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>4774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sexberget, Sexberget, Dlr</t>
+          <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493417</v>
+        <v>493301</v>
       </c>
       <c r="R21" t="n">
-        <v>6676274</v>
+        <v>6676186</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2926,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2936,12 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2956,22 +2952,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131338149</v>
+        <v>131332301</v>
       </c>
       <c r="B22" t="n">
-        <v>4773</v>
+        <v>8454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,42 +2975,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gräsberget, Gräsberget, Dlr</t>
+          <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493301</v>
+        <v>493388</v>
       </c>
       <c r="R22" t="n">
-        <v>6676186</v>
+        <v>6676299</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3043,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3053,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3068,127 +3064,15 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>131332301</v>
-      </c>
-      <c r="B23" t="n">
-        <v>8453</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Sexberget, Sexberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>493388</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6676299</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Karl Ericson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Karl Ericson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131349617</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131349603</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>131331459</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>131329935</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>131338781</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>131331376</v>
       </c>
       <c r="B9" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>131329898</v>
       </c>
       <c r="B10" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>131330689</v>
       </c>
       <c r="B12" t="n">
-        <v>92289</v>
+        <v>92292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131331292</v>
+        <v>131330685</v>
       </c>
       <c r="B13" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493340</v>
+        <v>493255</v>
       </c>
       <c r="R13" t="n">
-        <v>6676251</v>
+        <v>6676284</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2054,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131330685</v>
+        <v>131331292</v>
       </c>
       <c r="B14" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493255</v>
+        <v>493340</v>
       </c>
       <c r="R14" t="n">
-        <v>6676284</v>
+        <v>6676251</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2170,50 +2170,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131330910</v>
+        <v>131330084</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>5178</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493215</v>
+        <v>493092</v>
       </c>
       <c r="R15" t="n">
-        <v>6676275</v>
+        <v>6676215</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2245,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,6 +2268,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2275,61 +2280,57 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131330084</v>
+        <v>131330910</v>
       </c>
       <c r="B16" t="n">
-        <v>5178</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493092</v>
+        <v>493215</v>
       </c>
       <c r="R16" t="n">
-        <v>6676215</v>
+        <v>6676275</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2361,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,7 +2381,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
         <v>131338228</v>
       </c>
       <c r="B17" t="n">
-        <v>97275</v>
+        <v>97278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>131336740</v>
       </c>
       <c r="B18" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>131330626</v>
       </c>
       <c r="B19" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>131332454</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1363,53 +1363,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131330073</v>
+        <v>131331376</v>
       </c>
       <c r="B8" t="n">
-        <v>5178</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493086</v>
+        <v>493330</v>
       </c>
       <c r="R8" t="n">
-        <v>6676252</v>
+        <v>6676131</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,81 +1471,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131331376</v>
+        <v>131330073</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>5178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493330</v>
+        <v>493086</v>
       </c>
       <c r="R9" t="n">
-        <v>6676131</v>
+        <v>6676252</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,18 +1583,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131330685</v>
+        <v>131331292</v>
       </c>
       <c r="B13" t="n">
         <v>57090</v>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493255</v>
+        <v>493340</v>
       </c>
       <c r="R13" t="n">
-        <v>6676284</v>
+        <v>6676251</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2054,7 +2054,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131331292</v>
+        <v>131330685</v>
       </c>
       <c r="B14" t="n">
         <v>57090</v>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493340</v>
+        <v>493255</v>
       </c>
       <c r="R14" t="n">
-        <v>6676251</v>
+        <v>6676284</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2170,54 +2170,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131330084</v>
+        <v>131330910</v>
       </c>
       <c r="B15" t="n">
-        <v>5178</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493092</v>
+        <v>493215</v>
       </c>
       <c r="R15" t="n">
-        <v>6676215</v>
+        <v>6676275</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2249,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,7 +2264,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2280,57 +2275,61 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131330910</v>
+        <v>131330084</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>5178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493215</v>
+        <v>493092</v>
       </c>
       <c r="R16" t="n">
-        <v>6676275</v>
+        <v>6676215</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2362,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2371,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,6 +2380,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1363,62 +1363,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131331376</v>
+        <v>131330073</v>
       </c>
       <c r="B8" t="n">
-        <v>99038</v>
+        <v>5178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493330</v>
+        <v>493086</v>
       </c>
       <c r="R8" t="n">
-        <v>6676131</v>
+        <v>6676252</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,71 +1457,81 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131330073</v>
+        <v>131331376</v>
       </c>
       <c r="B9" t="n">
-        <v>5178</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493086</v>
+        <v>493330</v>
       </c>
       <c r="R9" t="n">
-        <v>6676252</v>
+        <v>6676131</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1570,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,19 +1584,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B17" t="n">
-        <v>97278</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R17" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2479,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>97278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,21 +2522,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R18" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2576,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131349617</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131349603</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>131331459</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>131329935</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>131338781</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>131331376</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>131329898</v>
       </c>
       <c r="B10" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>131330689</v>
       </c>
       <c r="B12" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>131331292</v>
       </c>
       <c r="B13" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131330685</v>
       </c>
       <c r="B14" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>131330910</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>97284</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R17" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B18" t="n">
-        <v>97278</v>
+        <v>79266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R18" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,7 +2621,7 @@
         <v>131330626</v>
       </c>
       <c r="B19" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>131332454</v>
       </c>
       <c r="B20" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>131331459</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>131329935</v>
       </c>
       <c r="B6" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>131338781</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131330073</v>
       </c>
       <c r="B8" t="n">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>131331376</v>
       </c>
       <c r="B9" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>131329898</v>
       </c>
       <c r="B10" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>131331158</v>
       </c>
       <c r="B11" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>131330689</v>
       </c>
       <c r="B12" t="n">
-        <v>92298</v>
+        <v>92301</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>131331292</v>
       </c>
       <c r="B13" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131330685</v>
       </c>
       <c r="B14" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>131330910</v>
       </c>
       <c r="B15" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>131330084</v>
       </c>
       <c r="B16" t="n">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B17" t="n">
-        <v>97284</v>
+        <v>79269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R17" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2479,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B18" t="n">
-        <v>79266</v>
+        <v>97287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,21 +2522,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R18" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2576,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,7 +2621,7 @@
         <v>131330626</v>
       </c>
       <c r="B19" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>131332454</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>131338149</v>
       </c>
       <c r="B21" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>131332301</v>
       </c>
       <c r="B22" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>131331459</v>
       </c>
       <c r="B5" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>131329935</v>
       </c>
       <c r="B6" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>131338781</v>
       </c>
       <c r="B7" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>131331376</v>
       </c>
       <c r="B9" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>131329898</v>
       </c>
       <c r="B10" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>131330689</v>
       </c>
       <c r="B12" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>131331292</v>
       </c>
       <c r="B13" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131330685</v>
       </c>
       <c r="B14" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>131330910</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B17" t="n">
-        <v>79269</v>
+        <v>97292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R17" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B18" t="n">
-        <v>97287</v>
+        <v>79274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R18" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,7 +2621,7 @@
         <v>131330626</v>
       </c>
       <c r="B19" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>131332454</v>
       </c>
       <c r="B20" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>131331459</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>131329935</v>
       </c>
       <c r="B6" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>131338781</v>
       </c>
       <c r="B7" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,53 +1363,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131330073</v>
+        <v>131331376</v>
       </c>
       <c r="B8" t="n">
-        <v>5179</v>
+        <v>99054</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493086</v>
+        <v>493330</v>
       </c>
       <c r="R8" t="n">
-        <v>6676252</v>
+        <v>6676131</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,81 +1471,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131331376</v>
+        <v>131330073</v>
       </c>
       <c r="B9" t="n">
-        <v>99052</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493330</v>
+        <v>493086</v>
       </c>
       <c r="R9" t="n">
-        <v>6676131</v>
+        <v>6676252</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,18 +1583,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1605,7 +1605,7 @@
         <v>131329898</v>
       </c>
       <c r="B10" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>131330689</v>
       </c>
       <c r="B12" t="n">
-        <v>92306</v>
+        <v>92308</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>131331292</v>
       </c>
       <c r="B13" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131330685</v>
       </c>
       <c r="B14" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>131330910</v>
       </c>
       <c r="B15" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>131338228</v>
       </c>
       <c r="B17" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>131336740</v>
       </c>
       <c r="B18" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>131330626</v>
       </c>
       <c r="B19" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>131332454</v>
       </c>
       <c r="B20" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B17" t="n">
-        <v>97294</v>
+        <v>79276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R17" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2479,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B18" t="n">
-        <v>79276</v>
+        <v>97294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,21 +2522,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R18" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2576,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B17" t="n">
-        <v>79276</v>
+        <v>97294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R17" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B18" t="n">
-        <v>97294</v>
+        <v>79276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R18" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1363,62 +1363,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131331376</v>
+        <v>131330073</v>
       </c>
       <c r="B8" t="n">
-        <v>99054</v>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493330</v>
+        <v>493086</v>
       </c>
       <c r="R8" t="n">
-        <v>6676131</v>
+        <v>6676252</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,71 +1457,81 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131330073</v>
+        <v>131331376</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>99054</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493086</v>
+        <v>493330</v>
       </c>
       <c r="R9" t="n">
-        <v>6676252</v>
+        <v>6676131</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1570,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,19 +1584,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2170,50 +2170,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131330910</v>
+        <v>131330084</v>
       </c>
       <c r="B15" t="n">
-        <v>57911</v>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493215</v>
+        <v>493092</v>
       </c>
       <c r="R15" t="n">
-        <v>6676275</v>
+        <v>6676215</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2245,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,6 +2268,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2275,61 +2280,57 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131330084</v>
+        <v>131330910</v>
       </c>
       <c r="B16" t="n">
-        <v>5179</v>
+        <v>57911</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493092</v>
+        <v>493215</v>
       </c>
       <c r="R16" t="n">
-        <v>6676215</v>
+        <v>6676275</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2361,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,7 +2381,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>131331459</v>
       </c>
       <c r="B5" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>131329935</v>
       </c>
       <c r="B6" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>131338781</v>
       </c>
       <c r="B7" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>131331376</v>
       </c>
       <c r="B9" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>131329898</v>
       </c>
       <c r="B10" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>131330689</v>
       </c>
       <c r="B12" t="n">
-        <v>92308</v>
+        <v>92344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>131331292</v>
       </c>
       <c r="B13" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131330685</v>
       </c>
       <c r="B14" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>131330910</v>
       </c>
       <c r="B16" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B17" t="n">
-        <v>79276</v>
+        <v>97330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R17" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B18" t="n">
-        <v>97294</v>
+        <v>79310</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R18" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,7 +2621,7 @@
         <v>131330626</v>
       </c>
       <c r="B19" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>131332454</v>
       </c>
       <c r="B20" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1123,7 +1123,7 @@
         <v>131329935</v>
       </c>
       <c r="B6" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,53 +1363,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131330073</v>
+        <v>131331376</v>
       </c>
       <c r="B8" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493086</v>
+        <v>493330</v>
       </c>
       <c r="R8" t="n">
-        <v>6676252</v>
+        <v>6676131</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,81 +1471,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131331376</v>
+        <v>131330073</v>
       </c>
       <c r="B9" t="n">
-        <v>99095</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493330</v>
+        <v>493086</v>
       </c>
       <c r="R9" t="n">
-        <v>6676131</v>
+        <v>6676252</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,18 +1583,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1834,7 +1834,7 @@
         <v>131330689</v>
       </c>
       <c r="B12" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B17" t="n">
-        <v>79315</v>
+        <v>97338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R17" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B18" t="n">
-        <v>97335</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R18" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1363,62 +1363,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131331376</v>
+        <v>131330073</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493330</v>
+        <v>493086</v>
       </c>
       <c r="R8" t="n">
-        <v>6676131</v>
+        <v>6676252</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,71 +1457,81 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131330073</v>
+        <v>131331376</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493086</v>
+        <v>493330</v>
       </c>
       <c r="R9" t="n">
-        <v>6676252</v>
+        <v>6676131</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1570,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,19 +1584,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2170,50 +2170,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131330910</v>
+        <v>131330084</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493215</v>
+        <v>493092</v>
       </c>
       <c r="R15" t="n">
-        <v>6676275</v>
+        <v>6676215</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2245,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,6 +2268,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2275,61 +2280,57 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131330084</v>
+        <v>131330910</v>
       </c>
       <c r="B16" t="n">
-        <v>5179</v>
+        <v>57945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493092</v>
+        <v>493215</v>
       </c>
       <c r="R16" t="n">
-        <v>6676215</v>
+        <v>6676275</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2361,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,7 +2381,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2392,17 +2392,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B17" t="n">
-        <v>97338</v>
+        <v>79317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R17" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2479,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>97338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,21 +2522,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R18" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2576,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -1363,53 +1363,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131330073</v>
+        <v>131331376</v>
       </c>
       <c r="B8" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493086</v>
+        <v>493330</v>
       </c>
       <c r="R8" t="n">
-        <v>6676252</v>
+        <v>6676131</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,81 +1471,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131331376</v>
+        <v>131330073</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493330</v>
+        <v>493086</v>
       </c>
       <c r="R9" t="n">
-        <v>6676131</v>
+        <v>6676252</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,18 +1583,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131336740</v>
+        <v>131338228</v>
       </c>
       <c r="B17" t="n">
-        <v>79317</v>
+        <v>97338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493320</v>
+        <v>493275</v>
       </c>
       <c r="R17" t="n">
-        <v>6676280</v>
+        <v>6676225</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131338228</v>
+        <v>131336740</v>
       </c>
       <c r="B18" t="n">
-        <v>97338</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493275</v>
+        <v>493320</v>
       </c>
       <c r="R18" t="n">
-        <v>6676225</v>
+        <v>6676280</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 7204-2026 artfynd.xlsx
+++ b/artfynd/A 7204-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131131591</v>
+        <v>131338228</v>
       </c>
       <c r="B2" t="n">
-        <v>57757</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100136</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gräsberget, Dlr</t>
+          <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493242</v>
+        <v>493275</v>
       </c>
       <c r="R2" t="n">
-        <v>6676200</v>
+        <v>6676225</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131349617</v>
+        <v>131330789</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>81355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,40 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräsberget, Dlr</t>
+          <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493016</v>
+        <v>493213</v>
       </c>
       <c r="R3" t="n">
-        <v>6676175</v>
+        <v>6676293</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,40 +850,49 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131349603</v>
+        <v>131330689</v>
       </c>
       <c r="B4" t="n">
-        <v>57901</v>
+        <v>92406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,45 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräsberget, Dlr</t>
+          <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493026</v>
+        <v>493258</v>
       </c>
       <c r="R4" t="n">
-        <v>6676165</v>
+        <v>6676286</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,14 +957,19 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosök nedtill på äldre gran.</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,62 +984,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131331459</v>
+        <v>131130554</v>
       </c>
       <c r="B5" t="n">
-        <v>57948</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gräsberget, Gräsberget, Dlr</t>
+          <t>Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493346</v>
+        <v>493112</v>
       </c>
       <c r="R5" t="n">
-        <v>6676152</v>
+        <v>6676222</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,27 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131329935</v>
+        <v>131131634</v>
       </c>
       <c r="B6" t="n">
-        <v>99098</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,48 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gräsberget, Gräsberget, Dlr</t>
+          <t>Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493073</v>
+        <v>493120</v>
       </c>
       <c r="R6" t="n">
-        <v>6676217</v>
+        <v>6676280</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,27 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Några bladrosetter</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,62 +1198,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131338781</v>
+        <v>131330149</v>
       </c>
       <c r="B7" t="n">
-        <v>57948</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493019</v>
+        <v>493107</v>
       </c>
       <c r="R7" t="n">
-        <v>6676199</v>
+        <v>6676222</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,12 +1290,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rätt gamla ringhack.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131331376</v>
+        <v>131330350</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,51 +1333,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493330</v>
+        <v>493119</v>
       </c>
       <c r="R8" t="n">
-        <v>6676131</v>
+        <v>6676282</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter.</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,65 +1417,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131330073</v>
+        <v>131336740</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493086</v>
+        <v>493320</v>
       </c>
       <c r="R9" t="n">
-        <v>6676252</v>
+        <v>6676280</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1509,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,72 +1523,69 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131329898</v>
+        <v>131349617</v>
       </c>
       <c r="B10" t="n">
-        <v>57136</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gräsberget, Gräsberget, Dlr</t>
+          <t>Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493071</v>
+        <v>493016</v>
       </c>
       <c r="R10" t="n">
-        <v>6676218</v>
+        <v>6676175</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,97 +1612,81 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Under tall</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131331158</v>
+        <v>131337684</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493288</v>
+        <v>493277</v>
       </c>
       <c r="R11" t="n">
-        <v>6676274</v>
+        <v>6676123</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,50 +1734,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131330689</v>
+        <v>131337746</v>
       </c>
       <c r="B12" t="n">
-        <v>92352</v>
+        <v>79992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1866,13 +1788,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493258</v>
+        <v>493272</v>
       </c>
       <c r="R12" t="n">
-        <v>6676286</v>
+        <v>6676120</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1901,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131331292</v>
+        <v>131330323</v>
       </c>
       <c r="B13" t="n">
-        <v>57136</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,41 +1871,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493340</v>
+        <v>493105</v>
       </c>
       <c r="R13" t="n">
-        <v>6676251</v>
+        <v>6676262</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,12 +1945,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,22 +1960,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131330685</v>
+        <v>131330910</v>
       </c>
       <c r="B14" t="n">
-        <v>57136</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,41 +1983,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493255</v>
+        <v>493215</v>
       </c>
       <c r="R14" t="n">
-        <v>6676284</v>
+        <v>6676275</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2128,7 +2047,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2057,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,22 +2072,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131330084</v>
+        <v>131331195</v>
       </c>
       <c r="B15" t="n">
-        <v>5179</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,43 +2095,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493092</v>
+        <v>493275</v>
       </c>
       <c r="R15" t="n">
-        <v>6676215</v>
+        <v>6676129</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2249,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,7 +2178,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2280,21 +2189,21 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131330910</v>
+        <v>131349603</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2316,24 +2225,27 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräsberget, Gräsberget, Dlr</t>
+          <t>Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493215</v>
+        <v>493026</v>
       </c>
       <c r="R16" t="n">
-        <v>6676275</v>
+        <v>6676165</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2360,19 +2272,14 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:28</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosök nedtill på äldre gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,22 +2294,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131338228</v>
+        <v>131130904</v>
       </c>
       <c r="B17" t="n">
-        <v>97338</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,34 +2317,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gräsberget, Gräsberget, Dlr</t>
+          <t>Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493275</v>
+        <v>493215</v>
       </c>
       <c r="R17" t="n">
-        <v>6676225</v>
+        <v>6676293</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2464,22 +2376,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,22 +2411,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131336740</v>
+        <v>131330714</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,37 +2434,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gräsberget, Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493320</v>
+        <v>493209</v>
       </c>
       <c r="R18" t="n">
-        <v>6676280</v>
+        <v>6676297</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2576,7 +2498,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2508,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2606,50 +2523,50 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131330626</v>
+        <v>131331459</v>
       </c>
       <c r="B19" t="n">
-        <v>57136</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2658,10 +2575,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493203</v>
+        <v>493346</v>
       </c>
       <c r="R19" t="n">
-        <v>6676289</v>
+        <v>6676152</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2693,7 +2610,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,12 +2620,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Under betad tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,7 +2655,7 @@
         <v>131332454</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2852,38 +2769,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131338149</v>
+        <v>131338781</v>
       </c>
       <c r="B21" t="n">
-        <v>4775</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2892,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493301</v>
+        <v>493019</v>
       </c>
       <c r="R21" t="n">
-        <v>6676186</v>
+        <v>6676199</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2927,7 +2844,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2854,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rätt gamla ringhack.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2952,65 +2874,70 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131332301</v>
+        <v>131131591</v>
       </c>
       <c r="B22" t="n">
-        <v>8455</v>
+        <v>57813</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100136</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sexberget, Sexberget, Dlr</t>
+          <t>Gräsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493388</v>
+        <v>493242</v>
       </c>
       <c r="R22" t="n">
-        <v>6676299</v>
+        <v>6676200</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3034,22 +2961,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,15 +2991,1523 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131329898</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>493071</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6676218</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Under tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>Karl Ericson</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Karl Ericson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131330626</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>493203</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6676289</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131330685</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>493255</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6676284</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131331292</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>493340</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6676251</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131338149</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>493301</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6676186</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131330073</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>493086</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6676252</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131330084</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>493092</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6676215</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Karl Ericson, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131331158</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>493288</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6676274</v>
+      </c>
+      <c r="S30" t="n">
+        <v>9</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131331200</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>493275</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6676130</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131332301</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sexberget, Sexberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>493388</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6676299</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131332498</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sexberget, Sexberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>493419</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6676236</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131329935</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>493073</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6676217</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Några bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131331376</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gräsberget, Gräsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>493330</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6676131</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
